--- a/GUA/Waste/A1_Outputs/A-O_AR_Projections_COMPLETED.xlsx
+++ b/GUA/Waste/A1_Outputs/A-O_AR_Projections_COMPLETED.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="125">
   <si>
     <t>Tech</t>
   </si>
@@ -48,31 +48,46 @@
     <t>NO_CONTR_OD</t>
   </si>
   <si>
+    <t>COPROC</t>
+  </si>
+  <si>
+    <t>INCIN</t>
+  </si>
+  <si>
+    <t>GAS_MSW</t>
+  </si>
+  <si>
+    <t>HTC</t>
+  </si>
+  <si>
     <t>OPEN_BURN</t>
   </si>
   <si>
     <t>SIT_CLAN</t>
   </si>
   <si>
-    <t>AERO_PTAR</t>
-  </si>
-  <si>
-    <t>AERO_PTAR_RU</t>
-  </si>
-  <si>
-    <t>ANAE_LAGN</t>
-  </si>
-  <si>
-    <t>ANAE_LAGN_RU</t>
-  </si>
-  <si>
-    <t>SEPT_SYST</t>
-  </si>
-  <si>
-    <t>LATR</t>
-  </si>
-  <si>
-    <t>EFLT_DISC</t>
+    <t>LANDFILL_ELEC</t>
+  </si>
+  <si>
+    <t>IND_SW</t>
+  </si>
+  <si>
+    <t>CO2_CH4_BURN</t>
+  </si>
+  <si>
+    <t>COMPOST_DOM</t>
+  </si>
+  <si>
+    <t>COMPOST_COFFEE</t>
+  </si>
+  <si>
+    <t>DWW_DC</t>
+  </si>
+  <si>
+    <t>DWW_N</t>
+  </si>
+  <si>
+    <t>IWW</t>
   </si>
   <si>
     <t>Recycling of separated inorganic waste at final disposal site</t>
@@ -90,31 +105,46 @@
     <t>Open dump</t>
   </si>
   <si>
+    <t>Coprocessing</t>
+  </si>
+  <si>
+    <t>Controlled incineration</t>
+  </si>
+  <si>
+    <t>Gasification of Municipal Solid Waste</t>
+  </si>
+  <si>
+    <t>Hydrothermal carbonization</t>
+  </si>
+  <si>
     <t>Open burning</t>
   </si>
   <si>
     <t>Disposal in clandestine sites</t>
   </si>
   <si>
-    <t>Centralized aerobic treatment plant</t>
-  </si>
-  <si>
-    <t>Reuse of treated water from centralized aerobic treatment plant</t>
-  </si>
-  <si>
-    <t>Anaerobic lagoon</t>
-  </si>
-  <si>
-    <t>Reuse of treated water from anaerobic lagoon</t>
-  </si>
-  <si>
-    <t>Septic system</t>
-  </si>
-  <si>
-    <t>Latrine</t>
-  </si>
-  <si>
-    <t>Effluent discharge to aquatic environment</t>
+    <t>Methane recovery in landfill to generate electricity</t>
+  </si>
+  <si>
+    <t>Industrial solid waste</t>
+  </si>
+  <si>
+    <t>Carbon dioxide from burning methane</t>
+  </si>
+  <si>
+    <t>Domestic compost</t>
+  </si>
+  <si>
+    <t>Agroindustrial compost</t>
+  </si>
+  <si>
+    <t>Domestic wastewater (degradable organic component)</t>
+  </si>
+  <si>
+    <t>Domestic wastewater (nitrogen)</t>
+  </si>
+  <si>
+    <t>Industrial waste water</t>
   </si>
   <si>
     <t>OSS_INORG</t>
@@ -129,12 +159,6 @@
     <t>NO_COLL_SDF</t>
   </si>
   <si>
-    <t>E1</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
     <t>Inorganic on site separation</t>
   </si>
   <si>
@@ -147,12 +171,6 @@
     <t>No collection on site separation</t>
   </si>
   <si>
-    <t>Stage 1</t>
-  </si>
-  <si>
-    <t>Stage 3</t>
-  </si>
-  <si>
     <t>OutputActivityRatio</t>
   </si>
   <si>
@@ -183,18 +201,6 @@
     <t>NO_SS</t>
   </si>
   <si>
-    <t>WWWT</t>
-  </si>
-  <si>
-    <t>WWWOT</t>
-  </si>
-  <si>
-    <t>SEWERWW</t>
-  </si>
-  <si>
-    <t>DIRECT_DISC</t>
-  </si>
-  <si>
     <t>Separation of inorganic waste in final disposal site</t>
   </si>
   <si>
@@ -228,18 +234,6 @@
     <t>No separation of waste in source</t>
   </si>
   <si>
-    <t>Waste water with treatement</t>
-  </si>
-  <si>
-    <t>Waste water without treatement</t>
-  </si>
-  <si>
-    <t>Collected waste water</t>
-  </si>
-  <si>
-    <t>Uncollected wastewater</t>
-  </si>
-  <si>
     <t>COLL_INORG</t>
   </si>
   <si>
@@ -264,15 +258,6 @@
     <t>TSW</t>
   </si>
   <si>
-    <t>E2</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>TWW</t>
-  </si>
-  <si>
     <t>Inorganic collection</t>
   </si>
   <si>
@@ -297,40 +282,115 @@
     <t>Total solid waste</t>
   </si>
   <si>
-    <t>Stage 2</t>
-  </si>
-  <si>
-    <t>Stage 4</t>
-  </si>
-  <si>
-    <t>Total waste water</t>
-  </si>
-  <si>
     <t>InputActivityRatio</t>
   </si>
   <si>
     <t>T5TSWTSW</t>
   </si>
   <si>
-    <t>T5TWWTWW</t>
+    <t>T5LANDFILL_ELECTSW</t>
+  </si>
+  <si>
+    <t>T5IND_SWTSW</t>
+  </si>
+  <si>
+    <t>T5CO2_CH4_BURNTSW</t>
+  </si>
+  <si>
+    <t>T5COMPOST_DOMTSW</t>
+  </si>
+  <si>
+    <t>T5COMPOST_COFFEETSW</t>
+  </si>
+  <si>
+    <t>T5DWW_DCWW</t>
+  </si>
+  <si>
+    <t>T5DWW_NWW</t>
+  </si>
+  <si>
+    <t>T5IWWWW</t>
   </si>
   <si>
     <t>Demand Total solid waste for Total solid waste</t>
   </si>
   <si>
-    <t>Demand Total waste water for Total waste water</t>
-  </si>
-  <si>
-    <t>E5_TSWTSW</t>
-  </si>
-  <si>
-    <t>E5_TWWTWW</t>
+    <t>Demand Methane recovery in landfill to generate electricity for Total solid waste</t>
+  </si>
+  <si>
+    <t>Demand Industrial solid waste for Total solid waste</t>
+  </si>
+  <si>
+    <t>Demand Carbon dioxide from burning methane for Total solid waste</t>
+  </si>
+  <si>
+    <t>Demand Domestic compost for Total solid waste</t>
+  </si>
+  <si>
+    <t>Demand Agroindustrial compost for Total solid waste</t>
+  </si>
+  <si>
+    <t>Demand Domestic wastewater (degradable organic component) for Waste water</t>
+  </si>
+  <si>
+    <t>Demand Domestic wastewater (nitrogen) for Waste water</t>
+  </si>
+  <si>
+    <t>Demand Industrial waste water for Waste water</t>
+  </si>
+  <si>
+    <t>E5TSWTSW</t>
+  </si>
+  <si>
+    <t>E5TSWLANDFILL_ELEC</t>
+  </si>
+  <si>
+    <t>E5TSWIND_SW</t>
+  </si>
+  <si>
+    <t>E5TSWCO2_CH4_BURN</t>
+  </si>
+  <si>
+    <t>E5TSWCOMPOST_DOM</t>
+  </si>
+  <si>
+    <t>E5TSWCOMPOST_COFFEE</t>
+  </si>
+  <si>
+    <t>E5WWDWW_DC</t>
+  </si>
+  <si>
+    <t>E5WWDWW_N</t>
+  </si>
+  <si>
+    <t>E5WWIWW</t>
   </si>
   <si>
     <t>Demand Total solid waste Total solid waste</t>
   </si>
   <si>
-    <t>Demand Total waste water Total waste water</t>
+    <t>Demand Total solid waste Methane recovery in landfill to generate electricity</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Industrial solid waste</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Carbon dioxide from burning methane</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Domestic compost</t>
+  </si>
+  <si>
+    <t>Demand Total solid waste Agroindustrial compost</t>
+  </si>
+  <si>
+    <t>Demand Waste water Domestic wastewater (degradable organic component)</t>
+  </si>
+  <si>
+    <t>Demand Waste water Domestic wastewater (nitrogen)</t>
+  </si>
+  <si>
+    <t>Demand Waste water Industrial waste water</t>
   </si>
 </sst>
 </file>
@@ -688,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL15"/>
+  <dimension ref="A1:AL20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -812,16 +872,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -928,16 +988,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -1044,16 +1104,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1160,16 +1220,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1276,16 +1336,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1392,16 +1452,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1508,16 +1568,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1624,16 +1684,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1740,16 +1800,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1856,16 +1916,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1972,16 +2032,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2088,16 +2148,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -2204,16 +2264,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -2320,114 +2380,694 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>1</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>1</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>1</v>
+      </c>
+      <c r="AI15">
+        <v>1</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>1</v>
+      </c>
+      <c r="AL15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
         <v>38</v>
       </c>
-      <c r="D15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15">
-        <v>1</v>
-      </c>
-      <c r="I15">
-        <v>1</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-      <c r="P15">
-        <v>1</v>
-      </c>
-      <c r="Q15">
-        <v>1</v>
-      </c>
-      <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="S15">
-        <v>1</v>
-      </c>
-      <c r="T15">
-        <v>1</v>
-      </c>
-      <c r="U15">
-        <v>1</v>
-      </c>
-      <c r="V15">
-        <v>1</v>
-      </c>
-      <c r="W15">
-        <v>1</v>
-      </c>
-      <c r="X15">
-        <v>1</v>
-      </c>
-      <c r="Y15">
-        <v>1</v>
-      </c>
-      <c r="Z15">
-        <v>1</v>
-      </c>
-      <c r="AA15">
-        <v>1</v>
-      </c>
-      <c r="AB15">
-        <v>1</v>
-      </c>
-      <c r="AC15">
-        <v>1</v>
-      </c>
-      <c r="AD15">
-        <v>1</v>
-      </c>
-      <c r="AE15">
-        <v>1</v>
-      </c>
-      <c r="AF15">
-        <v>1</v>
-      </c>
-      <c r="AG15">
-        <v>1</v>
-      </c>
-      <c r="AH15">
-        <v>1</v>
-      </c>
-      <c r="AI15">
-        <v>1</v>
-      </c>
-      <c r="AJ15">
-        <v>1</v>
-      </c>
-      <c r="AK15">
-        <v>1</v>
-      </c>
-      <c r="AL15">
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>1</v>
+      </c>
+      <c r="AB16">
+        <v>1</v>
+      </c>
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AD16">
+        <v>1</v>
+      </c>
+      <c r="AE16">
+        <v>1</v>
+      </c>
+      <c r="AF16">
+        <v>1</v>
+      </c>
+      <c r="AG16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>1</v>
+      </c>
+      <c r="AI16">
+        <v>1</v>
+      </c>
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>1</v>
+      </c>
+      <c r="AL16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>1</v>
+      </c>
+      <c r="AB17">
+        <v>1</v>
+      </c>
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AD17">
+        <v>1</v>
+      </c>
+      <c r="AE17">
+        <v>1</v>
+      </c>
+      <c r="AF17">
+        <v>1</v>
+      </c>
+      <c r="AG17">
+        <v>1</v>
+      </c>
+      <c r="AH17">
+        <v>1</v>
+      </c>
+      <c r="AI17">
+        <v>1</v>
+      </c>
+      <c r="AJ17">
+        <v>1</v>
+      </c>
+      <c r="AK17">
+        <v>1</v>
+      </c>
+      <c r="AL17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AE18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AG18">
+        <v>1</v>
+      </c>
+      <c r="AH18">
+        <v>1</v>
+      </c>
+      <c r="AI18">
+        <v>1</v>
+      </c>
+      <c r="AJ18">
+        <v>1</v>
+      </c>
+      <c r="AK18">
+        <v>1</v>
+      </c>
+      <c r="AL18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>1</v>
+      </c>
+      <c r="AB19">
+        <v>1</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>1</v>
+      </c>
+      <c r="AE19">
+        <v>1</v>
+      </c>
+      <c r="AF19">
+        <v>1</v>
+      </c>
+      <c r="AG19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
+        <v>1</v>
+      </c>
+      <c r="AI19">
+        <v>1</v>
+      </c>
+      <c r="AJ19">
+        <v>1</v>
+      </c>
+      <c r="AK19">
+        <v>1</v>
+      </c>
+      <c r="AL19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>1</v>
+      </c>
+      <c r="Y20">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>1</v>
+      </c>
+      <c r="AB20">
+        <v>1</v>
+      </c>
+      <c r="AC20">
+        <v>1</v>
+      </c>
+      <c r="AD20">
+        <v>1</v>
+      </c>
+      <c r="AE20">
+        <v>1</v>
+      </c>
+      <c r="AF20">
+        <v>1</v>
+      </c>
+      <c r="AG20">
+        <v>1</v>
+      </c>
+      <c r="AH20">
+        <v>1</v>
+      </c>
+      <c r="AI20">
+        <v>1</v>
+      </c>
+      <c r="AJ20">
+        <v>1</v>
+      </c>
+      <c r="AK20">
+        <v>1</v>
+      </c>
+      <c r="AL20">
         <v>1</v>
       </c>
     </row>
@@ -2438,7 +3078,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL31"/>
+  <dimension ref="A1:AL23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -2559,19 +3199,19 @@
     </row>
     <row r="2" spans="1:38">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2675,19 +3315,19 @@
     </row>
     <row r="3" spans="1:38">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2791,19 +3431,19 @@
     </row>
     <row r="4" spans="1:38">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -2907,19 +3547,19 @@
     </row>
     <row r="5" spans="1:38">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -3023,19 +3663,19 @@
     </row>
     <row r="6" spans="1:38">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -3139,19 +3779,19 @@
     </row>
     <row r="7" spans="1:38">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -3255,19 +3895,19 @@
     </row>
     <row r="8" spans="1:38">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -3371,19 +4011,19 @@
     </row>
     <row r="9" spans="1:38">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -3487,19 +4127,19 @@
     </row>
     <row r="10" spans="1:38">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -3603,19 +4243,19 @@
     </row>
     <row r="11" spans="1:38">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -3719,19 +4359,19 @@
     </row>
     <row r="12" spans="1:38">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -3835,19 +4475,19 @@
     </row>
     <row r="13" spans="1:38">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -3951,19 +4591,19 @@
     </row>
     <row r="14" spans="1:38">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -4067,19 +4707,19 @@
     </row>
     <row r="15" spans="1:38">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -4183,19 +4823,19 @@
     </row>
     <row r="16" spans="1:38">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
         <v>88</v>
-      </c>
-      <c r="E16" t="s">
-        <v>96</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -4299,19 +4939,19 @@
     </row>
     <row r="17" spans="1:38">
       <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" t="s">
         <v>51</v>
-      </c>
-      <c r="B17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" t="s">
-        <v>45</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -4415,19 +5055,19 @@
     </row>
     <row r="18" spans="1:38">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -4531,19 +5171,19 @@
     </row>
     <row r="19" spans="1:38">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -4647,19 +5287,19 @@
     </row>
     <row r="20" spans="1:38">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -4763,19 +5403,19 @@
     </row>
     <row r="21" spans="1:38">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -4879,19 +5519,19 @@
     </row>
     <row r="22" spans="1:38">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -4995,19 +5635,19 @@
     </row>
     <row r="23" spans="1:38">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -5106,934 +5746,6 @@
         <v>1</v>
       </c>
       <c r="AL23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:38">
-      <c r="A24" t="s">
-        <v>55</v>
-      </c>
-      <c r="B24" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" t="s">
-        <v>96</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24">
-        <v>1</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-      <c r="N24">
-        <v>1</v>
-      </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-      <c r="P24">
-        <v>1</v>
-      </c>
-      <c r="Q24">
-        <v>1</v>
-      </c>
-      <c r="R24">
-        <v>1</v>
-      </c>
-      <c r="S24">
-        <v>1</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-      <c r="U24">
-        <v>1</v>
-      </c>
-      <c r="V24">
-        <v>1</v>
-      </c>
-      <c r="W24">
-        <v>1</v>
-      </c>
-      <c r="X24">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>1</v>
-      </c>
-      <c r="Z24">
-        <v>1</v>
-      </c>
-      <c r="AA24">
-        <v>1</v>
-      </c>
-      <c r="AB24">
-        <v>1</v>
-      </c>
-      <c r="AC24">
-        <v>1</v>
-      </c>
-      <c r="AD24">
-        <v>1</v>
-      </c>
-      <c r="AE24">
-        <v>1</v>
-      </c>
-      <c r="AF24">
-        <v>1</v>
-      </c>
-      <c r="AG24">
-        <v>1</v>
-      </c>
-      <c r="AH24">
-        <v>1</v>
-      </c>
-      <c r="AI24">
-        <v>1</v>
-      </c>
-      <c r="AJ24">
-        <v>1</v>
-      </c>
-      <c r="AK24">
-        <v>1</v>
-      </c>
-      <c r="AL24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:38">
-      <c r="A25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D25" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" t="s">
-        <v>45</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25">
-        <v>1</v>
-      </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25">
-        <v>1</v>
-      </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <v>1</v>
-      </c>
-      <c r="P25">
-        <v>1</v>
-      </c>
-      <c r="Q25">
-        <v>1</v>
-      </c>
-      <c r="R25">
-        <v>1</v>
-      </c>
-      <c r="S25">
-        <v>1</v>
-      </c>
-      <c r="T25">
-        <v>1</v>
-      </c>
-      <c r="U25">
-        <v>1</v>
-      </c>
-      <c r="V25">
-        <v>1</v>
-      </c>
-      <c r="W25">
-        <v>1</v>
-      </c>
-      <c r="X25">
-        <v>1</v>
-      </c>
-      <c r="Y25">
-        <v>1</v>
-      </c>
-      <c r="Z25">
-        <v>1</v>
-      </c>
-      <c r="AA25">
-        <v>1</v>
-      </c>
-      <c r="AB25">
-        <v>1</v>
-      </c>
-      <c r="AC25">
-        <v>1</v>
-      </c>
-      <c r="AD25">
-        <v>1</v>
-      </c>
-      <c r="AE25">
-        <v>1</v>
-      </c>
-      <c r="AF25">
-        <v>1</v>
-      </c>
-      <c r="AG25">
-        <v>1</v>
-      </c>
-      <c r="AH25">
-        <v>1</v>
-      </c>
-      <c r="AI25">
-        <v>1</v>
-      </c>
-      <c r="AJ25">
-        <v>1</v>
-      </c>
-      <c r="AK25">
-        <v>1</v>
-      </c>
-      <c r="AL25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:38">
-      <c r="A26" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" t="s">
-        <v>38</v>
-      </c>
-      <c r="D26" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" t="s">
-        <v>96</v>
-      </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
-      <c r="I26">
-        <v>1</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26">
-        <v>1</v>
-      </c>
-      <c r="O26">
-        <v>1</v>
-      </c>
-      <c r="P26">
-        <v>1</v>
-      </c>
-      <c r="Q26">
-        <v>1</v>
-      </c>
-      <c r="R26">
-        <v>1</v>
-      </c>
-      <c r="S26">
-        <v>1</v>
-      </c>
-      <c r="T26">
-        <v>1</v>
-      </c>
-      <c r="U26">
-        <v>1</v>
-      </c>
-      <c r="V26">
-        <v>1</v>
-      </c>
-      <c r="W26">
-        <v>1</v>
-      </c>
-      <c r="X26">
-        <v>1</v>
-      </c>
-      <c r="Y26">
-        <v>1</v>
-      </c>
-      <c r="Z26">
-        <v>1</v>
-      </c>
-      <c r="AA26">
-        <v>1</v>
-      </c>
-      <c r="AB26">
-        <v>1</v>
-      </c>
-      <c r="AC26">
-        <v>1</v>
-      </c>
-      <c r="AD26">
-        <v>1</v>
-      </c>
-      <c r="AE26">
-        <v>1</v>
-      </c>
-      <c r="AF26">
-        <v>1</v>
-      </c>
-      <c r="AG26">
-        <v>1</v>
-      </c>
-      <c r="AH26">
-        <v>1</v>
-      </c>
-      <c r="AI26">
-        <v>1</v>
-      </c>
-      <c r="AJ26">
-        <v>1</v>
-      </c>
-      <c r="AK26">
-        <v>1</v>
-      </c>
-      <c r="AL26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:38">
-      <c r="A27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" t="s">
-        <v>83</v>
-      </c>
-      <c r="D27" t="s">
-        <v>94</v>
-      </c>
-      <c r="E27" t="s">
-        <v>45</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27">
-        <v>1</v>
-      </c>
-      <c r="I27">
-        <v>1</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
-      </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>1</v>
-      </c>
-      <c r="P27">
-        <v>1</v>
-      </c>
-      <c r="Q27">
-        <v>1</v>
-      </c>
-      <c r="R27">
-        <v>1</v>
-      </c>
-      <c r="S27">
-        <v>1</v>
-      </c>
-      <c r="T27">
-        <v>1</v>
-      </c>
-      <c r="U27">
-        <v>1</v>
-      </c>
-      <c r="V27">
-        <v>1</v>
-      </c>
-      <c r="W27">
-        <v>1</v>
-      </c>
-      <c r="X27">
-        <v>1</v>
-      </c>
-      <c r="Y27">
-        <v>1</v>
-      </c>
-      <c r="Z27">
-        <v>1</v>
-      </c>
-      <c r="AA27">
-        <v>1</v>
-      </c>
-      <c r="AB27">
-        <v>1</v>
-      </c>
-      <c r="AC27">
-        <v>1</v>
-      </c>
-      <c r="AD27">
-        <v>1</v>
-      </c>
-      <c r="AE27">
-        <v>1</v>
-      </c>
-      <c r="AF27">
-        <v>1</v>
-      </c>
-      <c r="AG27">
-        <v>1</v>
-      </c>
-      <c r="AH27">
-        <v>1</v>
-      </c>
-      <c r="AI27">
-        <v>1</v>
-      </c>
-      <c r="AJ27">
-        <v>1</v>
-      </c>
-      <c r="AK27">
-        <v>1</v>
-      </c>
-      <c r="AL27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:38">
-      <c r="A28" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" t="s">
-        <v>96</v>
-      </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28">
-        <v>1</v>
-      </c>
-      <c r="I28">
-        <v>1</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28">
-        <v>1</v>
-      </c>
-      <c r="O28">
-        <v>1</v>
-      </c>
-      <c r="P28">
-        <v>1</v>
-      </c>
-      <c r="Q28">
-        <v>1</v>
-      </c>
-      <c r="R28">
-        <v>1</v>
-      </c>
-      <c r="S28">
-        <v>1</v>
-      </c>
-      <c r="T28">
-        <v>1</v>
-      </c>
-      <c r="U28">
-        <v>1</v>
-      </c>
-      <c r="V28">
-        <v>1</v>
-      </c>
-      <c r="W28">
-        <v>1</v>
-      </c>
-      <c r="X28">
-        <v>1</v>
-      </c>
-      <c r="Y28">
-        <v>1</v>
-      </c>
-      <c r="Z28">
-        <v>1</v>
-      </c>
-      <c r="AA28">
-        <v>1</v>
-      </c>
-      <c r="AB28">
-        <v>1</v>
-      </c>
-      <c r="AC28">
-        <v>1</v>
-      </c>
-      <c r="AD28">
-        <v>1</v>
-      </c>
-      <c r="AE28">
-        <v>1</v>
-      </c>
-      <c r="AF28">
-        <v>1</v>
-      </c>
-      <c r="AG28">
-        <v>1</v>
-      </c>
-      <c r="AH28">
-        <v>1</v>
-      </c>
-      <c r="AI28">
-        <v>1</v>
-      </c>
-      <c r="AJ28">
-        <v>1</v>
-      </c>
-      <c r="AK28">
-        <v>1</v>
-      </c>
-      <c r="AL28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:38">
-      <c r="A29" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" t="s">
-        <v>45</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
-        <v>1</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
-      <c r="N29">
-        <v>1</v>
-      </c>
-      <c r="O29">
-        <v>1</v>
-      </c>
-      <c r="P29">
-        <v>1</v>
-      </c>
-      <c r="Q29">
-        <v>1</v>
-      </c>
-      <c r="R29">
-        <v>1</v>
-      </c>
-      <c r="S29">
-        <v>1</v>
-      </c>
-      <c r="T29">
-        <v>1</v>
-      </c>
-      <c r="U29">
-        <v>1</v>
-      </c>
-      <c r="V29">
-        <v>1</v>
-      </c>
-      <c r="W29">
-        <v>1</v>
-      </c>
-      <c r="X29">
-        <v>1</v>
-      </c>
-      <c r="Y29">
-        <v>1</v>
-      </c>
-      <c r="Z29">
-        <v>1</v>
-      </c>
-      <c r="AA29">
-        <v>1</v>
-      </c>
-      <c r="AB29">
-        <v>1</v>
-      </c>
-      <c r="AC29">
-        <v>1</v>
-      </c>
-      <c r="AD29">
-        <v>1</v>
-      </c>
-      <c r="AE29">
-        <v>1</v>
-      </c>
-      <c r="AF29">
-        <v>1</v>
-      </c>
-      <c r="AG29">
-        <v>1</v>
-      </c>
-      <c r="AH29">
-        <v>1</v>
-      </c>
-      <c r="AI29">
-        <v>1</v>
-      </c>
-      <c r="AJ29">
-        <v>1</v>
-      </c>
-      <c r="AK29">
-        <v>1</v>
-      </c>
-      <c r="AL29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:38">
-      <c r="A30" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" t="s">
-        <v>94</v>
-      </c>
-      <c r="E30" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-      <c r="I30">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
-      </c>
-      <c r="K30">
-        <v>1</v>
-      </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
-      <c r="M30">
-        <v>1</v>
-      </c>
-      <c r="N30">
-        <v>1</v>
-      </c>
-      <c r="O30">
-        <v>1</v>
-      </c>
-      <c r="P30">
-        <v>1</v>
-      </c>
-      <c r="Q30">
-        <v>1</v>
-      </c>
-      <c r="R30">
-        <v>1</v>
-      </c>
-      <c r="S30">
-        <v>1</v>
-      </c>
-      <c r="T30">
-        <v>1</v>
-      </c>
-      <c r="U30">
-        <v>1</v>
-      </c>
-      <c r="V30">
-        <v>1</v>
-      </c>
-      <c r="W30">
-        <v>1</v>
-      </c>
-      <c r="X30">
-        <v>1</v>
-      </c>
-      <c r="Y30">
-        <v>1</v>
-      </c>
-      <c r="Z30">
-        <v>1</v>
-      </c>
-      <c r="AA30">
-        <v>1</v>
-      </c>
-      <c r="AB30">
-        <v>1</v>
-      </c>
-      <c r="AC30">
-        <v>1</v>
-      </c>
-      <c r="AD30">
-        <v>1</v>
-      </c>
-      <c r="AE30">
-        <v>1</v>
-      </c>
-      <c r="AF30">
-        <v>1</v>
-      </c>
-      <c r="AG30">
-        <v>1</v>
-      </c>
-      <c r="AH30">
-        <v>1</v>
-      </c>
-      <c r="AI30">
-        <v>1</v>
-      </c>
-      <c r="AJ30">
-        <v>1</v>
-      </c>
-      <c r="AK30">
-        <v>1</v>
-      </c>
-      <c r="AL30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:38">
-      <c r="A31" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-      <c r="I31">
-        <v>1</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>1</v>
-      </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
-      <c r="N31">
-        <v>1</v>
-      </c>
-      <c r="O31">
-        <v>1</v>
-      </c>
-      <c r="P31">
-        <v>1</v>
-      </c>
-      <c r="Q31">
-        <v>1</v>
-      </c>
-      <c r="R31">
-        <v>1</v>
-      </c>
-      <c r="S31">
-        <v>1</v>
-      </c>
-      <c r="T31">
-        <v>1</v>
-      </c>
-      <c r="U31">
-        <v>1</v>
-      </c>
-      <c r="V31">
-        <v>1</v>
-      </c>
-      <c r="W31">
-        <v>1</v>
-      </c>
-      <c r="X31">
-        <v>1</v>
-      </c>
-      <c r="Y31">
-        <v>1</v>
-      </c>
-      <c r="Z31">
-        <v>1</v>
-      </c>
-      <c r="AA31">
-        <v>1</v>
-      </c>
-      <c r="AB31">
-        <v>1</v>
-      </c>
-      <c r="AC31">
-        <v>1</v>
-      </c>
-      <c r="AD31">
-        <v>1</v>
-      </c>
-      <c r="AE31">
-        <v>1</v>
-      </c>
-      <c r="AF31">
-        <v>1</v>
-      </c>
-      <c r="AG31">
-        <v>1</v>
-      </c>
-      <c r="AH31">
-        <v>1</v>
-      </c>
-      <c r="AI31">
-        <v>1</v>
-      </c>
-      <c r="AJ31">
-        <v>1</v>
-      </c>
-      <c r="AK31">
-        <v>1</v>
-      </c>
-      <c r="AL31">
         <v>1</v>
       </c>
     </row>
@@ -6044,7 +5756,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL5"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -6165,16 +5877,16 @@
     </row>
     <row r="2" spans="1:38">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -6278,19 +5990,19 @@
     </row>
     <row r="3" spans="1:38">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -6394,16 +6106,16 @@
     </row>
     <row r="4" spans="1:38">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -6507,375 +6219,1724 @@
     </row>
     <row r="5" spans="1:38">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>1</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+      <c r="AF5">
+        <v>1</v>
+      </c>
+      <c r="AG5">
+        <v>1</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <v>1</v>
+      </c>
+      <c r="AK5">
+        <v>1</v>
+      </c>
+      <c r="AL5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38">
+      <c r="A6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" t="s">
         <v>100</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>1</v>
+      </c>
+      <c r="AG6">
+        <v>1</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>1</v>
+      </c>
+      <c r="AK6">
+        <v>1</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38">
+      <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+      <c r="AF7">
+        <v>1</v>
+      </c>
+      <c r="AG7">
+        <v>1</v>
+      </c>
+      <c r="AH7">
+        <v>1</v>
+      </c>
+      <c r="AI7">
+        <v>1</v>
+      </c>
+      <c r="AJ7">
+        <v>1</v>
+      </c>
+      <c r="AK7">
+        <v>1</v>
+      </c>
+      <c r="AL7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38">
+      <c r="A8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
+      <c r="AG8">
+        <v>1</v>
+      </c>
+      <c r="AH8">
+        <v>1</v>
+      </c>
+      <c r="AI8">
+        <v>1</v>
+      </c>
+      <c r="AJ8">
+        <v>1</v>
+      </c>
+      <c r="AK8">
+        <v>1</v>
+      </c>
+      <c r="AL8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38">
+      <c r="A9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9">
+        <v>1</v>
+      </c>
+      <c r="AG9">
+        <v>1</v>
+      </c>
+      <c r="AH9">
+        <v>1</v>
+      </c>
+      <c r="AI9">
+        <v>1</v>
+      </c>
+      <c r="AJ9">
+        <v>1</v>
+      </c>
+      <c r="AK9">
+        <v>1</v>
+      </c>
+      <c r="AL9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38">
+      <c r="A10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" t="s">
         <v>102</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+      <c r="AF10">
+        <v>1</v>
+      </c>
+      <c r="AG10">
+        <v>1</v>
+      </c>
+      <c r="AH10">
+        <v>1</v>
+      </c>
+      <c r="AI10">
+        <v>1</v>
+      </c>
+      <c r="AJ10">
+        <v>1</v>
+      </c>
+      <c r="AK10">
+        <v>1</v>
+      </c>
+      <c r="AL10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38">
+      <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" t="s">
+        <v>120</v>
+      </c>
+      <c r="E11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>1</v>
+      </c>
+      <c r="AG11">
+        <v>1</v>
+      </c>
+      <c r="AH11">
+        <v>1</v>
+      </c>
+      <c r="AI11">
+        <v>1</v>
+      </c>
+      <c r="AJ11">
+        <v>1</v>
+      </c>
+      <c r="AK11">
+        <v>1</v>
+      </c>
+      <c r="AL11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38">
+      <c r="A12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12">
+        <v>1</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>1</v>
+      </c>
+      <c r="Y12">
+        <v>1</v>
+      </c>
+      <c r="Z12">
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>1</v>
+      </c>
+      <c r="AB12">
+        <v>1</v>
+      </c>
+      <c r="AC12">
+        <v>1</v>
+      </c>
+      <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AE12">
+        <v>1</v>
+      </c>
+      <c r="AF12">
+        <v>1</v>
+      </c>
+      <c r="AG12">
+        <v>1</v>
+      </c>
+      <c r="AH12">
+        <v>1</v>
+      </c>
+      <c r="AI12">
+        <v>1</v>
+      </c>
+      <c r="AJ12">
+        <v>1</v>
+      </c>
+      <c r="AK12">
+        <v>1</v>
+      </c>
+      <c r="AL12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38">
+      <c r="A13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13">
+        <v>1</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+      <c r="W13">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>1</v>
+      </c>
+      <c r="Y13">
+        <v>1</v>
+      </c>
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13">
+        <v>1</v>
+      </c>
+      <c r="AB13">
+        <v>1</v>
+      </c>
+      <c r="AC13">
+        <v>1</v>
+      </c>
+      <c r="AD13">
+        <v>1</v>
+      </c>
+      <c r="AE13">
+        <v>1</v>
+      </c>
+      <c r="AF13">
+        <v>1</v>
+      </c>
+      <c r="AG13">
+        <v>1</v>
+      </c>
+      <c r="AH13">
+        <v>1</v>
+      </c>
+      <c r="AI13">
+        <v>1</v>
+      </c>
+      <c r="AJ13">
+        <v>1</v>
+      </c>
+      <c r="AK13">
+        <v>1</v>
+      </c>
+      <c r="AL13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38">
+      <c r="A14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" t="s">
         <v>104</v>
       </c>
-      <c r="E5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-      <c r="W5">
-        <v>1</v>
-      </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <v>1</v>
-      </c>
-      <c r="Z5">
-        <v>1</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <v>1</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>1</v>
-      </c>
-      <c r="AE5">
-        <v>1</v>
-      </c>
-      <c r="AF5">
-        <v>1</v>
-      </c>
-      <c r="AG5">
-        <v>1</v>
-      </c>
-      <c r="AH5">
-        <v>1</v>
-      </c>
-      <c r="AI5">
-        <v>1</v>
-      </c>
-      <c r="AJ5">
-        <v>1</v>
-      </c>
-      <c r="AK5">
-        <v>1</v>
-      </c>
-      <c r="AL5">
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14">
+        <v>1</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+      <c r="W14">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>1</v>
+      </c>
+      <c r="Y14">
+        <v>1</v>
+      </c>
+      <c r="Z14">
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <v>1</v>
+      </c>
+      <c r="AB14">
+        <v>1</v>
+      </c>
+      <c r="AC14">
+        <v>1</v>
+      </c>
+      <c r="AD14">
+        <v>1</v>
+      </c>
+      <c r="AE14">
+        <v>1</v>
+      </c>
+      <c r="AF14">
+        <v>1</v>
+      </c>
+      <c r="AG14">
+        <v>1</v>
+      </c>
+      <c r="AH14">
+        <v>1</v>
+      </c>
+      <c r="AI14">
+        <v>1</v>
+      </c>
+      <c r="AJ14">
+        <v>1</v>
+      </c>
+      <c r="AK14">
+        <v>1</v>
+      </c>
+      <c r="AL14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38">
+      <c r="A15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>1</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+      <c r="W15">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>1</v>
+      </c>
+      <c r="Y15">
+        <v>1</v>
+      </c>
+      <c r="Z15">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>1</v>
+      </c>
+      <c r="AB15">
+        <v>1</v>
+      </c>
+      <c r="AC15">
+        <v>1</v>
+      </c>
+      <c r="AD15">
+        <v>1</v>
+      </c>
+      <c r="AE15">
+        <v>1</v>
+      </c>
+      <c r="AF15">
+        <v>1</v>
+      </c>
+      <c r="AG15">
+        <v>1</v>
+      </c>
+      <c r="AH15">
+        <v>1</v>
+      </c>
+      <c r="AI15">
+        <v>1</v>
+      </c>
+      <c r="AJ15">
+        <v>1</v>
+      </c>
+      <c r="AK15">
+        <v>1</v>
+      </c>
+      <c r="AL15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38">
+      <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16">
+        <v>1</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+      <c r="W16">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>1</v>
+      </c>
+      <c r="Y16">
+        <v>1</v>
+      </c>
+      <c r="Z16">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>1</v>
+      </c>
+      <c r="AB16">
+        <v>1</v>
+      </c>
+      <c r="AC16">
+        <v>1</v>
+      </c>
+      <c r="AD16">
+        <v>1</v>
+      </c>
+      <c r="AE16">
+        <v>1</v>
+      </c>
+      <c r="AF16">
+        <v>1</v>
+      </c>
+      <c r="AG16">
+        <v>1</v>
+      </c>
+      <c r="AH16">
+        <v>1</v>
+      </c>
+      <c r="AI16">
+        <v>1</v>
+      </c>
+      <c r="AJ16">
+        <v>1</v>
+      </c>
+      <c r="AK16">
+        <v>1</v>
+      </c>
+      <c r="AL16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38">
+      <c r="A17" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" t="s">
+        <v>105</v>
+      </c>
+      <c r="C17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>1</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>1</v>
+      </c>
+      <c r="Y17">
+        <v>1</v>
+      </c>
+      <c r="Z17">
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>1</v>
+      </c>
+      <c r="AB17">
+        <v>1</v>
+      </c>
+      <c r="AC17">
+        <v>1</v>
+      </c>
+      <c r="AD17">
+        <v>1</v>
+      </c>
+      <c r="AE17">
+        <v>1</v>
+      </c>
+      <c r="AF17">
+        <v>1</v>
+      </c>
+      <c r="AG17">
+        <v>1</v>
+      </c>
+      <c r="AH17">
+        <v>1</v>
+      </c>
+      <c r="AI17">
+        <v>1</v>
+      </c>
+      <c r="AJ17">
+        <v>1</v>
+      </c>
+      <c r="AK17">
+        <v>1</v>
+      </c>
+      <c r="AL17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38">
+      <c r="A18" t="s">
+        <v>97</v>
+      </c>
+      <c r="B18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>1</v>
+      </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>1</v>
+      </c>
+      <c r="AB18">
+        <v>1</v>
+      </c>
+      <c r="AC18">
+        <v>1</v>
+      </c>
+      <c r="AD18">
+        <v>1</v>
+      </c>
+      <c r="AE18">
+        <v>1</v>
+      </c>
+      <c r="AF18">
+        <v>1</v>
+      </c>
+      <c r="AG18">
+        <v>1</v>
+      </c>
+      <c r="AH18">
+        <v>1</v>
+      </c>
+      <c r="AI18">
+        <v>1</v>
+      </c>
+      <c r="AJ18">
+        <v>1</v>
+      </c>
+      <c r="AK18">
+        <v>1</v>
+      </c>
+      <c r="AL18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38">
+      <c r="A19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" t="s">
+        <v>124</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>1</v>
+      </c>
+      <c r="AB19">
+        <v>1</v>
+      </c>
+      <c r="AC19">
+        <v>1</v>
+      </c>
+      <c r="AD19">
+        <v>1</v>
+      </c>
+      <c r="AE19">
+        <v>1</v>
+      </c>
+      <c r="AF19">
+        <v>1</v>
+      </c>
+      <c r="AG19">
+        <v>1</v>
+      </c>
+      <c r="AH19">
+        <v>1</v>
+      </c>
+      <c r="AI19">
+        <v>1</v>
+      </c>
+      <c r="AJ19">
+        <v>1</v>
+      </c>
+      <c r="AK19">
+        <v>1</v>
+      </c>
+      <c r="AL19">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000360DE9767CDF0449BF75EAB371D3CB7" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="75cb9a07855af6ac97bd432464ca7c04">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" xmlns:ns3="081a93ea-d517-42a5-a2b7-457060aa7471" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d1676634304aab9936f6a5a5f53c7423" ns2:_="" ns3:_="">
-    <xsd:import namespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784"/>
-    <xsd:import namespace="081a93ea-d517-42a5-a2b7-457060aa7471"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="11" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="12" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="19" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="20" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="21" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="081a93ea-d517-42a5-a2b7-457060aa7471" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1fcbaaf-06d9-47c4-b3a2-beefbc45d784">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{572E8EAA-76AA-42EA-9039-E575BE7E480D}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF1B7FB0-15F6-4E97-9DC9-8AE724702783}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAE5ACE0-C127-4882-8781-CFD140F20CEC}"/>
 </file>